--- a/projects/abrir-candyshots/administracion/CandyShots-Administracion.xlsx
+++ b/projects/abrir-candyshots/administracion/CandyShots-Administracion.xlsx
@@ -854,12 +854,12 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>SI = tienes RUC régimen general y haces crédito tributario. NO = RIMPE/no facturas, el IVA es costo.</t>
+          <t>CONFIRMADO 2026-09-07: SI. Regimen general con RUC, credito tributario. Si eso cambia, ponlo en NO.</t>
         </is>
       </c>
     </row>
